--- a/Team-Data/2013-14/1-9-2013-14.xlsx
+++ b/Team-Data/2013-14/1-9-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -799,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -930,13 +997,13 @@
         <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -960,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -993,7 +1060,7 @@
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1115,7 +1182,7 @@
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1142,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1385,7 @@
         <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
         <v>8</v>
@@ -1348,7 +1415,7 @@
         <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1567,7 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
@@ -1664,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1676,7 +1743,7 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1953,67 +2020,67 @@
         <v>37.9</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="O9" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R9" t="n">
         <v>12.7</v>
       </c>
       <c r="S9" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="T9" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="U9" t="n">
         <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
         <v>7.3</v>
       </c>
       <c r="X9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AA9" t="n">
         <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2034,16 +2101,16 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL9" t="n">
         <v>15</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2058,13 +2125,13 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>14</v>
@@ -2073,10 +2140,10 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2686,7 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2631,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2771,7 +2838,7 @@
         <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3232,7 @@
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
@@ -3174,7 +3241,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>16</v>
@@ -3350,13 +3417,13 @@
         <v>27</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E17" t="n">
         <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.771</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.512</v>
+        <v>0.511</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
@@ -3421,34 +3488,34 @@
         <v>21.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.755</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="S17" t="n">
         <v>29.7</v>
       </c>
       <c r="T17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>15</v>
       </c>
       <c r="W17" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X17" t="n">
         <v>4.5</v>
@@ -3457,34 +3524,34 @@
         <v>2.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
         <v>21.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.5</v>
+        <v>104.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3502,13 +3569,13 @@
         <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3541,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="n">
         <v>15</v>
@@ -3848,13 +3915,13 @@
         <v>20</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>12</v>
@@ -3881,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
@@ -4030,7 +4097,7 @@
         <v>8</v>
       </c>
       <c r="AI20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
         <v>4</v>
@@ -4075,7 +4142,7 @@
         <v>7</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4119,106 +4186,106 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.371</v>
+        <v>0.353</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
         <v>83.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.436</v>
+        <v>0.433</v>
       </c>
       <c r="L21" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="P21" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.764</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T21" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="U21" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W21" t="n">
         <v>8.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y21" t="n">
         <v>3.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
       </c>
       <c r="AG21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI21" t="n">
         <v>23</v>
       </c>
-      <c r="AH21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>21</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4254,10 +4321,10 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
@@ -4266,10 +4333,10 @@
         <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4301,37 +4368,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>0.771</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="J22" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.467</v>
+        <v>0.47</v>
       </c>
       <c r="L22" t="n">
         <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O22" t="n">
         <v>21.1</v>
@@ -4343,7 +4410,7 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
         <v>35.9</v>
@@ -4352,52 +4419,52 @@
         <v>46.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.3</v>
+        <v>105.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4406,7 +4473,7 @@
         <v>22</v>
       </c>
       <c r="AM22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN22" t="n">
         <v>21</v>
@@ -4430,28 +4497,28 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
         <v>12</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="n">
         <v>25</v>
@@ -4788,7 +4855,7 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
@@ -4803,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4979,7 +5046,7 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -5113,10 +5180,10 @@
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
@@ -5140,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5152,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5383,7 @@
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5543,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
         <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5674,10 +5741,10 @@
         <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
         <v>28</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5874,7 +5941,7 @@
         <v>25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6105,7 @@
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-9-2013-14</t>
+          <t>2014-01-09</t>
         </is>
       </c>
     </row>
